--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124368281</v>
+        <v>124368689</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560607</v>
+        <v>560587</v>
       </c>
       <c r="R2" t="n">
-        <v>6676228</v>
+        <v>6676392</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124367758</v>
+        <v>124367376</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560446</v>
+        <v>560320</v>
       </c>
       <c r="R3" t="n">
-        <v>6676393</v>
+        <v>6676571</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124367376</v>
+        <v>124368381</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560320</v>
+        <v>560604</v>
       </c>
       <c r="R4" t="n">
-        <v>6676571</v>
+        <v>6676257</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124368689</v>
+        <v>124368981</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1017,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560587</v>
+        <v>560475</v>
       </c>
       <c r="R5" t="n">
-        <v>6676392</v>
+        <v>6676414</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124368827</v>
+        <v>124368281</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560475</v>
+        <v>560607</v>
       </c>
       <c r="R6" t="n">
-        <v>6676414</v>
+        <v>6676228</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368615</v>
+        <v>124367758</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1221,14 +1221,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560611</v>
+        <v>560446</v>
       </c>
       <c r="R7" t="n">
-        <v>6676376</v>
+        <v>6676393</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124368381</v>
+        <v>124368615</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560604</v>
+        <v>560611</v>
       </c>
       <c r="R8" t="n">
-        <v>6676257</v>
+        <v>6676376</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124368689</v>
+        <v>124368281</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560587</v>
+        <v>560607</v>
       </c>
       <c r="R2" t="n">
-        <v>6676392</v>
+        <v>6676228</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124368381</v>
+        <v>124368615</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560604</v>
+        <v>560611</v>
       </c>
       <c r="R4" t="n">
-        <v>6676257</v>
+        <v>6676376</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124368981</v>
+        <v>124368258</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560475</v>
+        <v>560446</v>
       </c>
       <c r="R5" t="n">
-        <v>6676414</v>
+        <v>6676393</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124368281</v>
+        <v>124368381</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560607</v>
+        <v>560604</v>
       </c>
       <c r="R6" t="n">
-        <v>6676228</v>
+        <v>6676257</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124367758</v>
+        <v>124368827</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560446</v>
+        <v>560475</v>
       </c>
       <c r="R7" t="n">
-        <v>6676393</v>
+        <v>6676414</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124368615</v>
+        <v>124368689</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560611</v>
+        <v>560587</v>
       </c>
       <c r="R8" t="n">
-        <v>6676376</v>
+        <v>6676392</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124368281</v>
+        <v>124368258</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560607</v>
+        <v>560446</v>
       </c>
       <c r="R2" t="n">
-        <v>6676228</v>
+        <v>6676393</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124367376</v>
+        <v>124367278</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124368615</v>
+        <v>124368827</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560611</v>
+        <v>560475</v>
       </c>
       <c r="R4" t="n">
-        <v>6676376</v>
+        <v>6676414</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124368258</v>
+        <v>124368381</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1017,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560446</v>
+        <v>560604</v>
       </c>
       <c r="R5" t="n">
-        <v>6676393</v>
+        <v>6676257</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124368381</v>
+        <v>124368281</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560604</v>
+        <v>560607</v>
       </c>
       <c r="R6" t="n">
-        <v>6676257</v>
+        <v>6676228</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368827</v>
+        <v>124368615</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1221,14 +1221,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560475</v>
+        <v>560611</v>
       </c>
       <c r="R7" t="n">
-        <v>6676414</v>
+        <v>6676376</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124368258</v>
+        <v>124368381</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560446</v>
+        <v>560604</v>
       </c>
       <c r="R2" t="n">
-        <v>6676393</v>
+        <v>6676257</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124367278</v>
+        <v>124368981</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560320</v>
+        <v>560475</v>
       </c>
       <c r="R3" t="n">
-        <v>6676571</v>
+        <v>6676414</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124368827</v>
+        <v>124368281</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560475</v>
+        <v>560607</v>
       </c>
       <c r="R4" t="n">
-        <v>6676414</v>
+        <v>6676228</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124368381</v>
+        <v>124367376</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1017,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560604</v>
+        <v>560320</v>
       </c>
       <c r="R5" t="n">
-        <v>6676257</v>
+        <v>6676571</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124368281</v>
+        <v>124368689</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560607</v>
+        <v>560587</v>
       </c>
       <c r="R6" t="n">
-        <v>6676228</v>
+        <v>6676392</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368615</v>
+        <v>124368258</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1221,14 +1221,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560611</v>
+        <v>560446</v>
       </c>
       <c r="R7" t="n">
-        <v>6676376</v>
+        <v>6676393</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124368689</v>
+        <v>124368615</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560587</v>
+        <v>560611</v>
       </c>
       <c r="R8" t="n">
-        <v>6676392</v>
+        <v>6676376</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124368381</v>
+        <v>124367278</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560604</v>
+        <v>560320</v>
       </c>
       <c r="R2" t="n">
-        <v>6676257</v>
+        <v>6676571</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124368981</v>
+        <v>124368615</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560475</v>
+        <v>560611</v>
       </c>
       <c r="R3" t="n">
-        <v>6676414</v>
+        <v>6676376</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124368281</v>
+        <v>124368981</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560607</v>
+        <v>560475</v>
       </c>
       <c r="R4" t="n">
-        <v>6676228</v>
+        <v>6676414</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124367376</v>
+        <v>124368381</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1017,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560320</v>
+        <v>560604</v>
       </c>
       <c r="R5" t="n">
-        <v>6676571</v>
+        <v>6676257</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124368689</v>
+        <v>124368258</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560587</v>
+        <v>560446</v>
       </c>
       <c r="R6" t="n">
-        <v>6676392</v>
+        <v>6676393</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368258</v>
+        <v>124368689</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1221,14 +1221,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560446</v>
+        <v>560587</v>
       </c>
       <c r="R7" t="n">
-        <v>6676393</v>
+        <v>6676392</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124368615</v>
+        <v>124368281</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560611</v>
+        <v>560607</v>
       </c>
       <c r="R8" t="n">
-        <v>6676376</v>
+        <v>6676228</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124367278</v>
+        <v>124367758</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560320</v>
+        <v>560446</v>
       </c>
       <c r="R2" t="n">
-        <v>6676571</v>
+        <v>6676393</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124368615</v>
+        <v>124367376</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560611</v>
+        <v>560320</v>
       </c>
       <c r="R3" t="n">
-        <v>6676376</v>
+        <v>6676571</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124368981</v>
+        <v>124368381</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560475</v>
+        <v>560604</v>
       </c>
       <c r="R4" t="n">
-        <v>6676414</v>
+        <v>6676257</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124368381</v>
+        <v>124368827</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1017,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560604</v>
+        <v>560475</v>
       </c>
       <c r="R5" t="n">
-        <v>6676257</v>
+        <v>6676414</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124368258</v>
+        <v>124368281</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560446</v>
+        <v>560607</v>
       </c>
       <c r="R6" t="n">
-        <v>6676393</v>
+        <v>6676228</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368689</v>
+        <v>124368615</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560587</v>
+        <v>560611</v>
       </c>
       <c r="R7" t="n">
-        <v>6676392</v>
+        <v>6676376</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124368281</v>
+        <v>124368689</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560607</v>
+        <v>560587</v>
       </c>
       <c r="R8" t="n">
-        <v>6676228</v>
+        <v>6676392</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124367758</v>
+        <v>124368615</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560446</v>
+        <v>560611</v>
       </c>
       <c r="R2" t="n">
-        <v>6676393</v>
+        <v>6676376</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124367376</v>
+        <v>124368689</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560320</v>
+        <v>560587</v>
       </c>
       <c r="R3" t="n">
-        <v>6676571</v>
+        <v>6676392</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124368381</v>
+        <v>124368827</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560604</v>
+        <v>560475</v>
       </c>
       <c r="R4" t="n">
-        <v>6676257</v>
+        <v>6676414</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124368827</v>
+        <v>124368381</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1017,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560475</v>
+        <v>560604</v>
       </c>
       <c r="R5" t="n">
-        <v>6676414</v>
+        <v>6676257</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124368281</v>
+        <v>124368258</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560607</v>
+        <v>560446</v>
       </c>
       <c r="R6" t="n">
-        <v>6676228</v>
+        <v>6676393</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368615</v>
+        <v>124368281</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560611</v>
+        <v>560607</v>
       </c>
       <c r="R7" t="n">
-        <v>6676376</v>
+        <v>6676228</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124368689</v>
+        <v>124367376</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1323,14 +1323,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560587</v>
+        <v>560320</v>
       </c>
       <c r="R8" t="n">
-        <v>6676392</v>
+        <v>6676571</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124368615</v>
+        <v>124367278</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560611</v>
+        <v>560320</v>
       </c>
       <c r="R2" t="n">
-        <v>6676376</v>
+        <v>6676571</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124368689</v>
+        <v>124368381</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560587</v>
+        <v>560604</v>
       </c>
       <c r="R3" t="n">
-        <v>6676392</v>
+        <v>6676257</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124368827</v>
+        <v>124368281</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560475</v>
+        <v>560607</v>
       </c>
       <c r="R4" t="n">
-        <v>6676414</v>
+        <v>6676228</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124368381</v>
+        <v>124368258</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1017,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560604</v>
+        <v>560446</v>
       </c>
       <c r="R5" t="n">
-        <v>6676257</v>
+        <v>6676393</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124368258</v>
+        <v>124368827</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560446</v>
+        <v>560475</v>
       </c>
       <c r="R6" t="n">
-        <v>6676393</v>
+        <v>6676414</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368281</v>
+        <v>124368615</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560607</v>
+        <v>560611</v>
       </c>
       <c r="R7" t="n">
-        <v>6676228</v>
+        <v>6676376</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124367376</v>
+        <v>124368689</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1323,14 +1323,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560320</v>
+        <v>560587</v>
       </c>
       <c r="R8" t="n">
-        <v>6676571</v>
+        <v>6676392</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124367278</v>
+        <v>124367376</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124368381</v>
+        <v>124368689</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560604</v>
+        <v>560587</v>
       </c>
       <c r="R3" t="n">
-        <v>6676257</v>
+        <v>6676392</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124368281</v>
+        <v>124368258</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560607</v>
+        <v>560446</v>
       </c>
       <c r="R4" t="n">
-        <v>6676228</v>
+        <v>6676393</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124368258</v>
+        <v>124368615</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1017,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560446</v>
+        <v>560611</v>
       </c>
       <c r="R5" t="n">
-        <v>6676393</v>
+        <v>6676376</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124368827</v>
+        <v>124368381</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560475</v>
+        <v>560604</v>
       </c>
       <c r="R6" t="n">
-        <v>6676414</v>
+        <v>6676257</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368615</v>
+        <v>124368981</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1221,14 +1221,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560611</v>
+        <v>560475</v>
       </c>
       <c r="R7" t="n">
-        <v>6676376</v>
+        <v>6676414</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124368689</v>
+        <v>124368281</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560587</v>
+        <v>560607</v>
       </c>
       <c r="R8" t="n">
-        <v>6676392</v>
+        <v>6676228</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124367376</v>
+        <v>124368281</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560320</v>
+        <v>560607</v>
       </c>
       <c r="R2" t="n">
-        <v>6676571</v>
+        <v>6676228</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124368689</v>
+        <v>124368981</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560587</v>
+        <v>560475</v>
       </c>
       <c r="R3" t="n">
-        <v>6676392</v>
+        <v>6676414</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124368258</v>
+        <v>124367758</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124368615</v>
+        <v>124368689</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560611</v>
+        <v>560587</v>
       </c>
       <c r="R5" t="n">
-        <v>6676376</v>
+        <v>6676392</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124368381</v>
+        <v>124367278</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560604</v>
+        <v>560320</v>
       </c>
       <c r="R6" t="n">
-        <v>6676257</v>
+        <v>6676571</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368981</v>
+        <v>124368615</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1221,14 +1221,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560475</v>
+        <v>560611</v>
       </c>
       <c r="R7" t="n">
-        <v>6676414</v>
+        <v>6676376</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124368281</v>
+        <v>124368381</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560607</v>
+        <v>560604</v>
       </c>
       <c r="R8" t="n">
-        <v>6676228</v>
+        <v>6676257</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124368281</v>
+        <v>124367278</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560607</v>
+        <v>560320</v>
       </c>
       <c r="R2" t="n">
-        <v>6676228</v>
+        <v>6676571</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124368981</v>
+        <v>124368281</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560475</v>
+        <v>560607</v>
       </c>
       <c r="R3" t="n">
-        <v>6676414</v>
+        <v>6676228</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124368689</v>
+        <v>124368827</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1017,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560587</v>
+        <v>560475</v>
       </c>
       <c r="R5" t="n">
-        <v>6676392</v>
+        <v>6676414</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124367278</v>
+        <v>124368615</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560320</v>
+        <v>560611</v>
       </c>
       <c r="R6" t="n">
-        <v>6676571</v>
+        <v>6676376</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368615</v>
+        <v>124368381</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560611</v>
+        <v>560604</v>
       </c>
       <c r="R7" t="n">
-        <v>6676376</v>
+        <v>6676257</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124368381</v>
+        <v>124368689</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560604</v>
+        <v>560587</v>
       </c>
       <c r="R8" t="n">
-        <v>6676257</v>
+        <v>6676392</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124367278</v>
+        <v>124367376</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124368281</v>
+        <v>124367758</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560607</v>
+        <v>560446</v>
       </c>
       <c r="R3" t="n">
-        <v>6676228</v>
+        <v>6676393</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124367758</v>
+        <v>124368615</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560446</v>
+        <v>560611</v>
       </c>
       <c r="R4" t="n">
-        <v>6676393</v>
+        <v>6676376</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124368827</v>
+        <v>124368281</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1017,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560475</v>
+        <v>560607</v>
       </c>
       <c r="R5" t="n">
-        <v>6676414</v>
+        <v>6676228</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124368615</v>
+        <v>124368981</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560611</v>
+        <v>560475</v>
       </c>
       <c r="R6" t="n">
-        <v>6676376</v>
+        <v>6676414</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368381</v>
+        <v>124368689</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560604</v>
+        <v>560587</v>
       </c>
       <c r="R7" t="n">
-        <v>6676257</v>
+        <v>6676392</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124368689</v>
+        <v>124368381</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560587</v>
+        <v>560604</v>
       </c>
       <c r="R8" t="n">
-        <v>6676392</v>
+        <v>6676257</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124367376</v>
+        <v>124367278</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124367758</v>
+        <v>124368689</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560446</v>
+        <v>560587</v>
       </c>
       <c r="R3" t="n">
-        <v>6676393</v>
+        <v>6676392</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124368615</v>
+        <v>124368981</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560611</v>
+        <v>560475</v>
       </c>
       <c r="R4" t="n">
-        <v>6676376</v>
+        <v>6676414</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124368281</v>
+        <v>124368258</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1017,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560607</v>
+        <v>560446</v>
       </c>
       <c r="R5" t="n">
-        <v>6676228</v>
+        <v>6676393</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124368981</v>
+        <v>124368615</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560475</v>
+        <v>560611</v>
       </c>
       <c r="R6" t="n">
-        <v>6676414</v>
+        <v>6676376</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368689</v>
+        <v>124368381</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560587</v>
+        <v>560604</v>
       </c>
       <c r="R7" t="n">
-        <v>6676392</v>
+        <v>6676257</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124368381</v>
+        <v>124368281</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560604</v>
+        <v>560607</v>
       </c>
       <c r="R8" t="n">
-        <v>6676257</v>
+        <v>6676228</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>124367278</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124368689</v>
+        <v>124367758</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560587</v>
+        <v>560446</v>
       </c>
       <c r="R3" t="n">
-        <v>6676392</v>
+        <v>6676393</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124368981</v>
+        <v>124368281</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560475</v>
+        <v>560607</v>
       </c>
       <c r="R4" t="n">
-        <v>6676414</v>
+        <v>6676228</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124368258</v>
+        <v>124368381</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,14 +997,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
+          <t>Hällsjön, Hällsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560446</v>
+        <v>560604</v>
       </c>
       <c r="R5" t="n">
-        <v>6676393</v>
+        <v>6676257</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,12 +1066,7 @@
         <v>124368615</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368381</v>
+        <v>124368689</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560604</v>
+        <v>560587</v>
       </c>
       <c r="R7" t="n">
-        <v>6676257</v>
+        <v>6676392</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124368281</v>
+        <v>124368827</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,14 +1288,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällsjön, Hällsjön, Dlr</t>
+          <t>Hällsjömossen, Hällsjömossen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560607</v>
+        <v>560475</v>
       </c>
       <c r="R8" t="n">
-        <v>6676228</v>
+        <v>6676414</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 17913-2025 artfynd.xlsx
+++ b/artfynd/A 17913-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124367278</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124367758</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124368281</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124368381</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124368615</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124368689</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,8 +1386,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124368827</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>